--- a/data/trans_orig/P65-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P65-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de empleados que tiene la empresa donde trabaja en 2007</t>
+          <t>Población según el número de empleados que tiene la empresa donde trabaja en 2007 (tasa de respuesta: 77,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11022</t>
+          <t>10802</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27008</t>
+          <t>26893</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>6082</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12071</t>
+          <t>12528</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28994</t>
+          <t>29901</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13280</t>
+          <t>12909</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31733</t>
+          <t>31234</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13209</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17909</t>
+          <t>19058</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38154</t>
+          <t>38646</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7677</t>
+          <t>7359</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20727</t>
+          <t>21286</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16821</t>
+          <t>17183</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15004</t>
+          <t>14826</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33224</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60430</t>
+          <t>61471</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93185</t>
+          <t>92231</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10701</t>
+          <t>11316</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25882</t>
+          <t>26183</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>77472</t>
+          <t>76665</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110204</t>
+          <t>113720</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90218</t>
+          <t>92438</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>125975</t>
+          <t>126187</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33461</t>
+          <t>33626</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>54057</t>
+          <t>56465</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>132143</t>
+          <t>132605</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>172013</t>
+          <t>171202</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,67%</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56768</t>
+          <t>56601</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>86796</t>
+          <t>87376</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37684</t>
+          <t>36964</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59524</t>
+          <t>59478</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>98527</t>
+          <t>98621</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>138971</t>
+          <t>136193</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39047</t>
+          <t>39789</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67125</t>
+          <t>66699</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18257</t>
+          <t>17847</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38044</t>
+          <t>36616</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>62443</t>
+          <t>64042</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>98080</t>
+          <t>99229</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47902</t>
+          <t>46887</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>80032</t>
+          <t>78207</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17360</t>
+          <t>17572</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38211</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>69105</t>
+          <t>70526</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>106870</t>
+          <t>109724</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45628</t>
+          <t>45887</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78725</t>
+          <t>76993</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18903</t>
+          <t>20160</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>42046</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71417</t>
+          <t>71279</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>110250</t>
+          <t>110046</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>204905</t>
+          <t>208517</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>261063</t>
+          <t>258763</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60094</t>
+          <t>60310</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>91205</t>
+          <t>89928</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>280806</t>
+          <t>278321</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>339791</t>
+          <t>338985</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>342279</t>
+          <t>344218</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>402939</t>
+          <t>404885</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>175574</t>
+          <t>174884</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>220619</t>
+          <t>218236</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>532190</t>
+          <t>535682</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>608473</t>
+          <t>605844</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,72%</t>
         </is>
       </c>
     </row>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>95715</t>
+          <t>94048</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>137438</t>
+          <t>135235</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>88717</t>
+          <t>89492</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>126692</t>
+          <t>125545</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>196384</t>
+          <t>192651</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>255337</t>
+          <t>252204</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32295</t>
+          <t>31884</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>58561</t>
+          <t>58321</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16377</t>
+          <t>16758</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34937</t>
+          <t>36220</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>52813</t>
+          <t>52728</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>86634</t>
+          <t>86564</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26620</t>
+          <t>26928</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50988</t>
+          <t>49934</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14989</t>
+          <t>15387</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33431</t>
+          <t>33312</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46328</t>
+          <t>46806</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77003</t>
+          <t>77416</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,34%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21953</t>
+          <t>21855</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43447</t>
+          <t>43373</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12970</t>
+          <t>12624</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30573</t>
+          <t>30338</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>38315</t>
+          <t>38784</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>67915</t>
+          <t>66912</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>47387</t>
+          <t>50059</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>77232</t>
+          <t>77887</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>37003</t>
+          <t>35033</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>60371</t>
+          <t>59991</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>89556</t>
+          <t>91796</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>128513</t>
+          <t>128862</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,54%</t>
         </is>
       </c>
     </row>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>80371</t>
+          <t>79976</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>113373</t>
+          <t>112682</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>51273</t>
+          <t>51017</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>78078</t>
+          <t>76930</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>138223</t>
+          <t>138025</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>180091</t>
+          <t>182268</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>36,12%</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26107</t>
+          <t>27713</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>51521</t>
+          <t>51611</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11899</t>
+          <t>10952</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>28096</t>
+          <t>28100</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>43330</t>
+          <t>41977</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>72839</t>
+          <t>71894</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>92625</t>
+          <t>92200</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>136877</t>
+          <t>135382</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>40517</t>
+          <t>39970</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>69440</t>
+          <t>67071</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>140052</t>
+          <t>143313</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>192203</t>
+          <t>190664</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>97798</t>
+          <t>98101</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>143340</t>
+          <t>142072</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>42995</t>
+          <t>42069</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>72554</t>
+          <t>72297</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>151507</t>
+          <t>149971</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>203993</t>
+          <t>203467</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>86627</t>
+          <t>86390</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>128078</t>
+          <t>126828</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>44740</t>
+          <t>45802</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>74127</t>
+          <t>75798</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>140220</t>
+          <t>140460</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>190775</t>
+          <t>192649</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>335243</t>
+          <t>333456</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>404709</t>
+          <t>402591</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3472,82 +3472,82 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>22,17%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>26,76%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>139735</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>118326</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>159446</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>17,76%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>15,04%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>20,27%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>510658</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>469045</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>549995</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
           <t>22,29%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>26,9%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>139735</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>116635</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>160380</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>17,76%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>14,83%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>20,39%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>510658</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>471736</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>552552</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>22,29%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>536201</t>
+          <t>537512</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>615882</t>
+          <t>613784</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>278916</t>
+          <t>278476</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>336154</t>
+          <t>332525</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>838334</t>
+          <t>834153</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>928757</t>
+          <t>929023</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3655,12 +3655,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,55%</t>
         </is>
       </c>
     </row>
@@ -3683,12 +3683,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>196831</t>
+          <t>195412</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>252585</t>
+          <t>249710</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>147428</t>
+          <t>151958</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>199094</t>
+          <t>199346</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,12 +3753,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>361613</t>
+          <t>360198</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>431498</t>
+          <t>433467</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -3949,7 +3949,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de empleados que tiene la empresa donde trabaja en 2012</t>
+          <t>Población según el número de empleados que tiene la empresa donde trabaja en 2012 (tasa de respuesta: 88,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5241</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>922</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8394</t>
+          <t>8009</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12273</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6288</t>
+          <t>6383</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20155</t>
+          <t>20218</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10370</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27048</t>
+          <t>27737</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9870</t>
+          <t>10025</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>958</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8556</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3205</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14082</t>
+          <t>14460</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17005</t>
+          <t>18293</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36821</t>
+          <t>36658</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13290</t>
+          <t>14075</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31402</t>
+          <t>32051</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36404</t>
+          <t>36344</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63117</t>
+          <t>62940</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -4596,12 +4596,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>57675</t>
+          <t>59139</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84995</t>
+          <t>83528</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28565</t>
+          <t>28450</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50425</t>
+          <t>50096</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>93548</t>
+          <t>95005</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>127544</t>
+          <t>129216</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>42,3%</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53402</t>
+          <t>53416</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>78518</t>
+          <t>79067</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4724,12 +4724,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42062</t>
+          <t>40939</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>65284</t>
+          <t>64514</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4759,12 +4759,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>101998</t>
+          <t>100021</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>136040</t>
+          <t>135595</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,38%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64945</t>
+          <t>64496</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>101328</t>
+          <t>99823</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21832</t>
+          <t>21437</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44692</t>
+          <t>44960</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>92800</t>
+          <t>93359</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>137642</t>
+          <t>136244</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44063</t>
+          <t>44936</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>77487</t>
+          <t>78170</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22880</t>
+          <t>22619</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46747</t>
+          <t>47493</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>73757</t>
+          <t>75324</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>115422</t>
+          <t>113191</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -5165,12 +5165,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24512</t>
+          <t>24917</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48213</t>
+          <t>47261</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27344</t>
+          <t>27340</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51669</t>
+          <t>53736</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58512</t>
+          <t>57771</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91939</t>
+          <t>93793</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -5278,12 +5278,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>132653</t>
+          <t>132219</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>177887</t>
+          <t>175966</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>43984</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>73377</t>
+          <t>74542</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>184716</t>
+          <t>184616</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>242675</t>
+          <t>238584</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>17,92%</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>300363</t>
+          <t>299155</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>361206</t>
+          <t>357282</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181935</t>
+          <t>181933</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>227239</t>
+          <t>228302</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>495554</t>
+          <t>498177</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>569606</t>
+          <t>570835</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>42,88%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>139661</t>
+          <t>139285</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>187097</t>
+          <t>186290</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>125371</t>
+          <t>126029</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>167362</t>
+          <t>168459</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>278690</t>
+          <t>280947</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>340336</t>
+          <t>345451</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,95%</t>
         </is>
       </c>
     </row>
@@ -5734,12 +5734,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26236</t>
+          <t>24985</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50285</t>
+          <t>50220</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22716</t>
+          <t>22363</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43436</t>
+          <t>43541</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>53851</t>
+          <t>55063</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>85636</t>
+          <t>87954</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,36%</t>
         </is>
       </c>
     </row>
@@ -5847,12 +5847,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15429</t>
+          <t>15457</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36162</t>
+          <t>36126</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7392</t>
+          <t>6936</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20792</t>
+          <t>20415</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25166</t>
+          <t>26288</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49366</t>
+          <t>49694</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -5960,12 +5960,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13565</t>
+          <t>13927</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32116</t>
+          <t>32436</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5019</t>
+          <t>5640</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20618</t>
+          <t>21482</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>23403</t>
+          <t>23017</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>46354</t>
+          <t>47065</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -6073,12 +6073,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>44343</t>
+          <t>42813</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>70474</t>
+          <t>71260</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>36107</t>
+          <t>36329</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>60883</t>
+          <t>61144</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>84785</t>
+          <t>85863</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>122243</t>
+          <t>123014</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,07%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>72199</t>
+          <t>72756</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>105408</t>
+          <t>104258</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35595</t>
+          <t>36212</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61124</t>
+          <t>60621</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>115766</t>
+          <t>118116</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>156558</t>
+          <t>159712</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>35,15%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28602</t>
+          <t>28752</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>55309</t>
+          <t>54715</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>23799</t>
+          <t>23689</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>46239</t>
+          <t>46673</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>58049</t>
+          <t>58962</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>92459</t>
+          <t>95862</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -6529,12 +6529,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>95499</t>
+          <t>96552</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>139918</t>
+          <t>143386</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6564,12 +6564,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>53112</t>
+          <t>52885</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>87568</t>
+          <t>85091</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6599,12 +6599,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>157381</t>
+          <t>157172</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>213471</t>
+          <t>210748</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
@@ -6642,12 +6642,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>71829</t>
+          <t>72162</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>112020</t>
+          <t>111671</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6677,12 +6677,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>44118</t>
+          <t>43564</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>72389</t>
+          <t>72576</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>124722</t>
+          <t>124528</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>173505</t>
+          <t>175587</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>45814</t>
+          <t>46227</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>76701</t>
+          <t>77766</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6790,12 +6790,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>39107</t>
+          <t>39749</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>70116</t>
+          <t>71018</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6825,12 +6825,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>93502</t>
+          <t>94647</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>137079</t>
+          <t>135873</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -6868,12 +6868,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>208065</t>
+          <t>207563</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>267316</t>
+          <t>265555</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>106829</t>
+          <t>106499</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>150168</t>
+          <t>151100</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>326248</t>
+          <t>328097</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>399366</t>
+          <t>400390</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,15%</t>
         </is>
       </c>
     </row>
@@ -6981,12 +6981,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>456600</t>
+          <t>456121</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>527465</t>
+          <t>525785</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>264394</t>
+          <t>263037</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>319068</t>
+          <t>322777</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>734614</t>
+          <t>734566</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>829284</t>
+          <t>827258</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,56%</t>
         </is>
       </c>
     </row>
@@ -7094,12 +7094,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>240685</t>
+          <t>241481</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>299235</t>
+          <t>302467</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7109,12 +7109,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7129,12 +7129,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>207737</t>
+          <t>207016</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>263208</t>
+          <t>262604</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7164,12 +7164,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>462011</t>
+          <t>462248</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>540588</t>
+          <t>546679</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,14%</t>
         </is>
       </c>
     </row>
@@ -7360,7 +7360,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de empleados que tiene la empresa donde trabaja en 2016</t>
+          <t>Población según el número de empleados que tiene la empresa donde trabaja en 2016 (tasa de respuesta: 89,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11483</t>
+          <t>10874</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5711</t>
+          <t>5611</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13203</t>
+          <t>13696</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -7668,12 +7668,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14829</t>
+          <t>14036</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7683,12 +7683,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7703,12 +7703,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10632</t>
+          <t>10347</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7067</t>
+          <t>6402</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>20046</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -7781,12 +7781,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12264</t>
+          <t>11858</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7796,12 +7796,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3747</t>
+          <t>3844</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13357</t>
+          <t>14186</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7851,12 +7851,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>7531</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21377</t>
+          <t>22193</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -7894,12 +7894,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24489</t>
+          <t>24078</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44114</t>
+          <t>45181</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7909,12 +7909,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7929,12 +7929,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>4976</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16206</t>
+          <t>16092</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7964,12 +7964,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32804</t>
+          <t>32245</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55348</t>
+          <t>56303</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,54%</t>
         </is>
       </c>
     </row>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35593</t>
+          <t>35074</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58633</t>
+          <t>56586</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8022,12 +8022,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11053</t>
+          <t>11116</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24809</t>
+          <t>24835</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>50561</t>
+          <t>50472</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>76870</t>
+          <t>75772</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,09%</t>
         </is>
       </c>
     </row>
@@ -8120,12 +8120,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15565</t>
+          <t>16141</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>33822</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8155,12 +8155,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15758</t>
+          <t>14282</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30419</t>
+          <t>29393</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>34052</t>
+          <t>34592</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>57859</t>
+          <t>58656</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,81%</t>
         </is>
       </c>
     </row>
@@ -8350,12 +8350,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61283</t>
+          <t>61660</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>96918</t>
+          <t>95919</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8365,12 +8365,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8385,12 +8385,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34594</t>
+          <t>35164</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63306</t>
+          <t>63089</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8400,12 +8400,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>104682</t>
+          <t>104325</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>147887</t>
+          <t>147620</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -8463,12 +8463,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35140</t>
+          <t>34244</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>62055</t>
+          <t>62842</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8498,12 +8498,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18372</t>
+          <t>17223</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38465</t>
+          <t>36897</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>57819</t>
+          <t>58696</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>91551</t>
+          <t>92959</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -8576,12 +8576,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31307</t>
+          <t>31066</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57324</t>
+          <t>56878</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22404</t>
+          <t>23155</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46877</t>
+          <t>47041</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58729</t>
+          <t>59561</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94315</t>
+          <t>94761</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -8689,12 +8689,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>172382</t>
+          <t>168627</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>222712</t>
+          <t>220057</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8704,12 +8704,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>85476</t>
+          <t>85846</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>122847</t>
+          <t>122301</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>269516</t>
+          <t>269217</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>332815</t>
+          <t>332158</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>323063</t>
+          <t>323842</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>381285</t>
+          <t>382175</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8817,12 +8817,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8837,12 +8837,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>221204</t>
+          <t>218502</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>267503</t>
+          <t>265598</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8852,12 +8852,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8872,12 +8872,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>554946</t>
+          <t>555338</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>628530</t>
+          <t>630273</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8887,12 +8887,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,94%</t>
         </is>
       </c>
     </row>
@@ -8915,12 +8915,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>117274</t>
+          <t>116258</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>160745</t>
+          <t>160289</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8930,12 +8930,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8950,12 +8950,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>109004</t>
+          <t>109596</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>147977</t>
+          <t>147778</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8985,12 +8985,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>235536</t>
+          <t>235759</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>298093</t>
+          <t>294481</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9000,12 +9000,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,53%</t>
         </is>
       </c>
     </row>
@@ -9145,12 +9145,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>51294</t>
+          <t>50578</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>80289</t>
+          <t>78064</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9160,12 +9160,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9180,12 +9180,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44884</t>
+          <t>44903</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>73761</t>
+          <t>72664</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>104010</t>
+          <t>103091</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>143117</t>
+          <t>143357</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,19%</t>
         </is>
       </c>
     </row>
@@ -9258,12 +9258,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9445</t>
+          <t>10023</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28076</t>
+          <t>28146</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9273,12 +9273,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9293,12 +9293,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12436</t>
+          <t>12654</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30119</t>
+          <t>29439</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9308,12 +9308,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9328,12 +9328,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27167</t>
+          <t>26378</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51397</t>
+          <t>50282</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -9371,12 +9371,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22162</t>
+          <t>22447</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44667</t>
+          <t>45028</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9386,12 +9386,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9406,12 +9406,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23067</t>
+          <t>22977</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9441,12 +9441,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>35033</t>
+          <t>35505</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>60677</t>
+          <t>61836</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9456,12 +9456,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -9484,12 +9484,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51202</t>
+          <t>52161</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>82979</t>
+          <t>82529</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9499,12 +9499,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9519,12 +9519,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>54669</t>
+          <t>54678</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>83263</t>
+          <t>83778</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9539,7 +9539,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9554,12 +9554,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>113669</t>
+          <t>113306</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>154809</t>
+          <t>153895</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9569,12 +9569,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,04%</t>
         </is>
       </c>
     </row>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>69997</t>
+          <t>71220</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>104045</t>
+          <t>103028</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9632,12 +9632,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>60679</t>
+          <t>61382</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91630</t>
+          <t>91538</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9647,12 +9647,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>140381</t>
+          <t>140097</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>182650</t>
+          <t>183944</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,33%</t>
         </is>
       </c>
     </row>
@@ -9710,12 +9710,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28722</t>
+          <t>29802</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>55539</t>
+          <t>53834</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9725,12 +9725,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>18749</t>
+          <t>18344</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>37811</t>
+          <t>38107</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9760,12 +9760,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9780,12 +9780,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>52116</t>
+          <t>53556</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>83715</t>
+          <t>84790</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -9940,12 +9940,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>125103</t>
+          <t>125433</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>172043</t>
+          <t>170875</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9955,12 +9955,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9975,12 +9975,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>89962</t>
+          <t>89071</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>131467</t>
+          <t>129788</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9990,12 +9990,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>225304</t>
+          <t>225667</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>283501</t>
+          <t>286009</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -10053,12 +10053,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>56373</t>
+          <t>56499</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>89629</t>
+          <t>92513</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10088,12 +10088,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>39057</t>
+          <t>38828</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>67354</t>
+          <t>67683</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10103,12 +10103,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>102542</t>
+          <t>104535</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>146184</t>
+          <t>146780</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -10166,12 +10166,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>62578</t>
+          <t>62822</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>99179</t>
+          <t>100035</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10181,12 +10181,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>41471</t>
+          <t>42287</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>72004</t>
+          <t>72128</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10216,12 +10216,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>115278</t>
+          <t>113645</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>161906</t>
+          <t>160381</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -10279,12 +10279,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>261883</t>
+          <t>262438</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>326042</t>
+          <t>321924</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10294,12 +10294,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>156474</t>
+          <t>158213</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>206028</t>
+          <t>206556</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10329,12 +10329,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10349,12 +10349,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>437363</t>
+          <t>435683</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>512931</t>
+          <t>515037</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10364,12 +10364,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>449689</t>
+          <t>446012</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>518378</t>
+          <t>518819</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10427,12 +10427,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>309904</t>
+          <t>306927</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>365517</t>
+          <t>366366</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10442,12 +10442,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10462,12 +10462,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>776296</t>
+          <t>770960</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>863687</t>
+          <t>867043</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10477,12 +10477,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,63%</t>
         </is>
       </c>
     </row>
@@ -10505,12 +10505,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>175067</t>
+          <t>178506</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>231177</t>
+          <t>228517</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10520,12 +10520,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10540,12 +10540,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>152689</t>
+          <t>152938</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>201458</t>
+          <t>201267</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10555,12 +10555,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10575,12 +10575,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>344009</t>
+          <t>342613</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>413964</t>
+          <t>414946</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10590,12 +10590,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -10771,7 +10771,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de empleados que tiene la empresa donde trabaja en 2023</t>
+          <t>Población según el número de empleados que tiene la empresa donde trabaja en 2023 (tasa de respuesta: 83,06%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10966,12 +10966,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11876</t>
+          <t>11228</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10981,12 +10981,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11001,12 +11001,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>8023</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11016,12 +11016,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11036,12 +11036,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3826</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15037</t>
+          <t>15026</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11051,12 +11051,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -11079,12 +11079,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>10323</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11094,12 +11094,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11114,12 +11114,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6966</t>
+          <t>6611</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11129,12 +11129,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11149,12 +11149,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14297</t>
+          <t>14537</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11164,12 +11164,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -11192,12 +11192,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17532</t>
+          <t>17399</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11207,12 +11207,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11227,12 +11227,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8733</t>
+          <t>9293</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11242,12 +11242,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11262,12 +11262,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7349</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22108</t>
+          <t>21918</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11277,12 +11277,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -11305,12 +11305,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32295</t>
+          <t>32962</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56573</t>
+          <t>55828</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6680</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17423</t>
+          <t>17464</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11355,12 +11355,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11375,12 +11375,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43087</t>
+          <t>42001</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69118</t>
+          <t>70379</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11390,12 +11390,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,98%</t>
         </is>
       </c>
     </row>
@@ -11418,12 +11418,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29253</t>
+          <t>28594</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51588</t>
+          <t>50240</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11453,12 +11453,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16625</t>
+          <t>16055</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31150</t>
+          <t>30699</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11468,12 +11468,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11488,12 +11488,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>50436</t>
+          <t>50742</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>76196</t>
+          <t>77597</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11503,12 +11503,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>39,67%</t>
         </is>
       </c>
     </row>
@@ -11531,12 +11531,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13024</t>
+          <t>13553</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29729</t>
+          <t>32324</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11566,12 +11566,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20814</t>
+          <t>21927</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39735</t>
+          <t>40206</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11601,12 +11601,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>38052</t>
+          <t>38110</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>65156</t>
+          <t>65631</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11616,12 +11616,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,55%</t>
         </is>
       </c>
     </row>
@@ -11761,12 +11761,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82059</t>
+          <t>83323</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>123360</t>
+          <t>121712</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11796,12 +11796,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51326</t>
+          <t>50486</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>88740</t>
+          <t>90042</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11811,12 +11811,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11831,12 +11831,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>142120</t>
+          <t>142318</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>201946</t>
+          <t>199824</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11846,12 +11846,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -11874,12 +11874,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43743</t>
+          <t>43469</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>81131</t>
+          <t>78184</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11909,12 +11909,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36820</t>
+          <t>37302</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>69951</t>
+          <t>69127</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11924,12 +11924,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11944,12 +11944,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>89793</t>
+          <t>90910</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>136454</t>
+          <t>138609</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11959,12 +11959,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -11987,12 +11987,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95257</t>
+          <t>95162</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>141002</t>
+          <t>140426</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12022,12 +12022,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43239</t>
+          <t>44384</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79051</t>
+          <t>79382</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12037,12 +12037,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>149211</t>
+          <t>149116</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>206391</t>
+          <t>209131</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12072,12 +12072,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -12100,12 +12100,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>264005</t>
+          <t>265301</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>331018</t>
+          <t>330484</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12115,12 +12115,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12135,12 +12135,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>155142</t>
+          <t>153247</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>276181</t>
+          <t>283203</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12150,12 +12150,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12170,12 +12170,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>432621</t>
+          <t>433026</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>578058</t>
+          <t>568745</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12185,12 +12185,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,64%</t>
         </is>
       </c>
     </row>
@@ -12213,12 +12213,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>257719</t>
+          <t>253864</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>321190</t>
+          <t>321213</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -12248,12 +12248,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>223311</t>
+          <t>220104</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>435293</t>
+          <t>434551</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12263,12 +12263,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12283,12 +12283,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>503552</t>
+          <t>506438</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>724215</t>
+          <t>723078</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12298,12 +12298,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,22%</t>
         </is>
       </c>
     </row>
@@ -12326,12 +12326,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>123857</t>
+          <t>122893</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>169829</t>
+          <t>171524</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12341,12 +12341,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12361,12 +12361,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>87004</t>
+          <t>83027</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>145366</t>
+          <t>144290</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>229146</t>
+          <t>228675</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>300048</t>
+          <t>302504</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -12556,12 +12556,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>65545</t>
+          <t>64625</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>100248</t>
+          <t>99208</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12571,12 +12571,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12591,12 +12591,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>59280</t>
+          <t>60080</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>85244</t>
+          <t>87783</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12606,12 +12606,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12626,12 +12626,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>131360</t>
+          <t>132712</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>174884</t>
+          <t>175369</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12641,12 +12641,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,94%</t>
         </is>
       </c>
     </row>
@@ -12669,12 +12669,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20516</t>
+          <t>20579</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61957</t>
+          <t>68926</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12684,12 +12684,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12704,12 +12704,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21131</t>
+          <t>21637</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39833</t>
+          <t>40574</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12719,12 +12719,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12739,12 +12739,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47457</t>
+          <t>46951</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>92603</t>
+          <t>91976</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12754,12 +12754,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -12782,12 +12782,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20725</t>
+          <t>21454</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43641</t>
+          <t>45651</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12797,12 +12797,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12817,12 +12817,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20235</t>
+          <t>20678</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38951</t>
+          <t>38619</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12832,12 +12832,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12852,12 +12852,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>45375</t>
+          <t>46480</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>75660</t>
+          <t>76871</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12867,12 +12867,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -12895,12 +12895,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>82298</t>
+          <t>81534</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>120671</t>
+          <t>122681</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12910,12 +12910,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>70699</t>
+          <t>71122</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>97356</t>
+          <t>96986</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12945,12 +12945,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -12965,12 +12965,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>161156</t>
+          <t>161879</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>207136</t>
+          <t>206735</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12980,12 +12980,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,23%</t>
         </is>
       </c>
     </row>
@@ -13008,12 +13008,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52154</t>
+          <t>52485</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>86231</t>
+          <t>85409</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13023,12 +13023,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13043,12 +13043,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>72440</t>
+          <t>72046</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>102202</t>
+          <t>102724</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13078,12 +13078,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>134166</t>
+          <t>133361</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>176985</t>
+          <t>178331</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -13121,12 +13121,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>49727</t>
+          <t>48372</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>78814</t>
+          <t>79864</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13136,12 +13136,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>44570</t>
+          <t>43560</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>67138</t>
+          <t>67896</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13191,12 +13191,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>99776</t>
+          <t>99730</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>139191</t>
+          <t>137929</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -13351,12 +13351,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>162952</t>
+          <t>159541</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>217277</t>
+          <t>215654</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13386,12 +13386,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>118963</t>
+          <t>113301</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>171656</t>
+          <t>169906</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13401,12 +13401,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13421,12 +13421,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>298139</t>
+          <t>298727</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>370565</t>
+          <t>370656</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13436,12 +13436,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -13464,12 +13464,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>76991</t>
+          <t>77071</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>131927</t>
+          <t>131727</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13479,12 +13479,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13499,12 +13499,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>67593</t>
+          <t>67367</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>104261</t>
+          <t>103853</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13514,12 +13514,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13534,12 +13534,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>156072</t>
+          <t>153603</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>221364</t>
+          <t>217627</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13549,12 +13549,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -13577,12 +13577,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>132391</t>
+          <t>133470</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>183440</t>
+          <t>183199</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13592,12 +13592,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -13612,12 +13612,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>76935</t>
+          <t>75916</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>115518</t>
+          <t>114679</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13627,12 +13627,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -13647,12 +13647,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>218170</t>
+          <t>215981</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>285555</t>
+          <t>285533</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -13690,12 +13690,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>400177</t>
+          <t>402234</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>480605</t>
+          <t>483272</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13705,12 +13705,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13725,12 +13725,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>244629</t>
+          <t>243392</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>384051</t>
+          <t>368760</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13760,12 +13760,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>667443</t>
+          <t>670314</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>825609</t>
+          <t>823235</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,2%</t>
         </is>
       </c>
     </row>
@@ -13803,12 +13803,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>361720</t>
+          <t>358239</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>436114</t>
+          <t>435836</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13818,12 +13818,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>332347</t>
+          <t>332657</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>553437</t>
+          <t>558070</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13873,12 +13873,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>713925</t>
+          <t>719397</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>981738</t>
+          <t>968063</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -13916,12 +13916,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>198180</t>
+          <t>199714</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>260494</t>
+          <t>259824</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13931,12 +13931,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>167877</t>
+          <t>167124</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>232428</t>
+          <t>235028</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13986,12 +13986,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>384360</t>
+          <t>386218</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>473738</t>
+          <t>473601</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P65-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P65-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10802</t>
+          <t>10556</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26893</t>
+          <t>27317</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6082</t>
+          <t>6518</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12528</t>
+          <t>11951</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29901</t>
+          <t>29165</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12909</t>
+          <t>13360</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31234</t>
+          <t>32026</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12459</t>
+          <t>12257</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19058</t>
+          <t>17820</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38646</t>
+          <t>39523</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7359</t>
+          <t>7050</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21286</t>
+          <t>20198</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>4164</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17183</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14826</t>
+          <t>14236</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>32826</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61471</t>
+          <t>60803</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92231</t>
+          <t>92724</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11316</t>
+          <t>11032</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26183</t>
+          <t>26040</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>76665</t>
+          <t>74870</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113720</t>
+          <t>109857</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>92438</t>
+          <t>89867</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>126187</t>
+          <t>125181</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33626</t>
+          <t>33828</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>56465</t>
+          <t>55679</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>132605</t>
+          <t>131663</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>171202</t>
+          <t>171894</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56601</t>
+          <t>56410</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>87376</t>
+          <t>85570</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36964</t>
+          <t>37425</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59478</t>
+          <t>59619</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>98621</t>
+          <t>100064</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>136193</t>
+          <t>137569</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,88%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39789</t>
+          <t>38137</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66699</t>
+          <t>66571</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17847</t>
+          <t>17533</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36616</t>
+          <t>37803</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>64042</t>
+          <t>62862</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>99229</t>
+          <t>97337</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>46887</t>
+          <t>44669</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>78207</t>
+          <t>78081</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,49 +1656,49 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>8,75%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>27112</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>19343</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>40563</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>5,86%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>4,18%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
           <t>8,77%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>27112</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>17572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>38211</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>5,86%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>3,8%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>8,26%</t>
-        </is>
-      </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>82</t>
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>70526</t>
+          <t>71504</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>109724</t>
+          <t>107575</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45887</t>
+          <t>45681</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76993</t>
+          <t>78084</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20160</t>
+          <t>19898</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42046</t>
+          <t>41337</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71279</t>
+          <t>72190</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>110046</t>
+          <t>110315</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>208517</t>
+          <t>208699</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>258763</t>
+          <t>261135</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60310</t>
+          <t>60907</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>89928</t>
+          <t>93216</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>278321</t>
+          <t>278694</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>338985</t>
+          <t>341080</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,18%</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>344218</t>
+          <t>342306</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>404885</t>
+          <t>402438</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>174884</t>
+          <t>176637</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>218236</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>535682</t>
+          <t>531921</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>605844</t>
+          <t>606513</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,77%</t>
         </is>
       </c>
     </row>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>94048</t>
+          <t>95823</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>135235</t>
+          <t>135491</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>89492</t>
+          <t>87238</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>125545</t>
+          <t>125559</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>192651</t>
+          <t>194204</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>252204</t>
+          <t>248420</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31884</t>
+          <t>32909</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>58321</t>
+          <t>59187</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16758</t>
+          <t>15135</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>36220</t>
+          <t>35334</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>52728</t>
+          <t>52665</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>86564</t>
+          <t>85815</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,01%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26928</t>
+          <t>26307</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49934</t>
+          <t>51028</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15387</t>
+          <t>14832</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33312</t>
+          <t>33048</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46806</t>
+          <t>47537</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77416</t>
+          <t>76555</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21855</t>
+          <t>21683</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43373</t>
+          <t>44662</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12624</t>
+          <t>12944</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30338</t>
+          <t>30598</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>38784</t>
+          <t>38098</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>66912</t>
+          <t>67723</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>50059</t>
+          <t>47152</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>77887</t>
+          <t>76263</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>35033</t>
+          <t>35581</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>59991</t>
+          <t>60804</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>91796</t>
+          <t>92139</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>128862</t>
+          <t>129009</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,57%</t>
         </is>
       </c>
     </row>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>79976</t>
+          <t>78218</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>112682</t>
+          <t>111074</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>51017</t>
+          <t>50676</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>76930</t>
+          <t>78014</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>138025</t>
+          <t>139143</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>182268</t>
+          <t>180182</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>35,71%</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>27713</t>
+          <t>26495</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>51611</t>
+          <t>52012</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10952</t>
+          <t>11350</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>28100</t>
+          <t>28908</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>41977</t>
+          <t>43924</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>71894</t>
+          <t>74003</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,67%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>92200</t>
+          <t>93396</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>135382</t>
+          <t>136228</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39970</t>
+          <t>40750</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>68842</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>143313</t>
+          <t>142079</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>190664</t>
+          <t>192676</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>98101</t>
+          <t>97146</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>142072</t>
+          <t>141603</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>42069</t>
+          <t>43231</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>72297</t>
+          <t>71962</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>149971</t>
+          <t>148552</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>203467</t>
+          <t>201494</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>86390</t>
+          <t>84453</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>126828</t>
+          <t>126451</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>45802</t>
+          <t>46095</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>75798</t>
+          <t>76720</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>140460</t>
+          <t>139908</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>192649</t>
+          <t>189954</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>333456</t>
+          <t>337799</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>402591</t>
+          <t>403593</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>118326</t>
+          <t>119988</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>159446</t>
+          <t>162830</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>469045</t>
+          <t>473033</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>549995</t>
+          <t>553176</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>537512</t>
+          <t>534745</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>613784</t>
+          <t>613868</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>278476</t>
+          <t>280127</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>332525</t>
+          <t>332383</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>834153</t>
+          <t>836934</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>929023</t>
+          <t>931102</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3655,12 +3655,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,64%</t>
         </is>
       </c>
     </row>
@@ -3683,12 +3683,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>195412</t>
+          <t>193075</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>249710</t>
+          <t>249251</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>151958</t>
+          <t>150391</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>199346</t>
+          <t>197991</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,12 +3753,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>360198</t>
+          <t>356422</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>433467</t>
+          <t>432860</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5241</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7024</t>
+          <t>6867</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>931</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8009</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>2720</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12000</t>
+          <t>12341</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6383</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20218</t>
+          <t>19981</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10370</t>
+          <t>10643</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27737</t>
+          <t>26937</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10025</t>
+          <t>10484</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9085</t>
+          <t>8513</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3068</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14460</t>
+          <t>13940</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18293</t>
+          <t>18160</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36658</t>
+          <t>36362</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14075</t>
+          <t>14124</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32051</t>
+          <t>31797</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36344</t>
+          <t>38170</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62940</t>
+          <t>64164</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -4596,12 +4596,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>59139</t>
+          <t>59652</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>83528</t>
+          <t>85606</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28450</t>
+          <t>29117</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50096</t>
+          <t>50384</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>95005</t>
+          <t>94004</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>129216</t>
+          <t>126903</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>41,54%</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53416</t>
+          <t>52764</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>79067</t>
+          <t>79880</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4724,12 +4724,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40939</t>
+          <t>40073</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>64514</t>
+          <t>63952</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4759,12 +4759,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>100021</t>
+          <t>100414</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>135595</t>
+          <t>134003</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>43,86%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64496</t>
+          <t>63044</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>99823</t>
+          <t>99592</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21437</t>
+          <t>21923</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44960</t>
+          <t>44584</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>93359</t>
+          <t>92325</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>136244</t>
+          <t>134328</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44936</t>
+          <t>45168</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>78170</t>
+          <t>77607</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22619</t>
+          <t>22130</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>47493</t>
+          <t>46640</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>75324</t>
+          <t>74833</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>113191</t>
+          <t>115183</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -5165,12 +5165,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24917</t>
+          <t>23496</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47261</t>
+          <t>46295</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27340</t>
+          <t>27183</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53736</t>
+          <t>52176</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57771</t>
+          <t>57415</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93793</t>
+          <t>91663</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -5278,12 +5278,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>132219</t>
+          <t>132003</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>175966</t>
+          <t>177833</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43984</t>
+          <t>44962</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74542</t>
+          <t>73992</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>184616</t>
+          <t>184289</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>238584</t>
+          <t>240819</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>299155</t>
+          <t>296776</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>357282</t>
+          <t>357720</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181933</t>
+          <t>184201</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>228302</t>
+          <t>230279</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>498177</t>
+          <t>498715</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>570835</t>
+          <t>575312</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>43,22%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>139285</t>
+          <t>140329</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>186290</t>
+          <t>187471</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>126029</t>
+          <t>123613</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>168459</t>
+          <t>167144</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>280947</t>
+          <t>280428</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>345451</t>
+          <t>342751</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,75%</t>
         </is>
       </c>
     </row>
@@ -5734,12 +5734,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24985</t>
+          <t>25651</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50220</t>
+          <t>49467</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22363</t>
+          <t>22777</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43541</t>
+          <t>44337</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>55063</t>
+          <t>54035</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>87954</t>
+          <t>85507</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -5847,12 +5847,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15457</t>
+          <t>16324</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36126</t>
+          <t>36361</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6936</t>
+          <t>7565</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20415</t>
+          <t>20976</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26288</t>
+          <t>26138</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49694</t>
+          <t>49803</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -5960,12 +5960,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13927</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32436</t>
+          <t>33099</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5640</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21482</t>
+          <t>20244</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>23017</t>
+          <t>22438</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>47065</t>
+          <t>46546</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -6073,12 +6073,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>42813</t>
+          <t>43039</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>71260</t>
+          <t>71632</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>36329</t>
+          <t>36347</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>61144</t>
+          <t>59665</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>85863</t>
+          <t>86829</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>123014</t>
+          <t>122989</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>72756</t>
+          <t>73324</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>104258</t>
+          <t>106630</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36212</t>
+          <t>35865</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60621</t>
+          <t>60855</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>118116</t>
+          <t>117964</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>159712</t>
+          <t>160271</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,27%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28752</t>
+          <t>29078</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>54715</t>
+          <t>55455</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>23689</t>
+          <t>24978</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>46673</t>
+          <t>48431</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>58962</t>
+          <t>58706</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>95862</t>
+          <t>95022</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,91%</t>
         </is>
       </c>
     </row>
@@ -6529,12 +6529,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>96552</t>
+          <t>93737</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>143386</t>
+          <t>139557</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6564,12 +6564,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52885</t>
+          <t>51527</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>85091</t>
+          <t>83834</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6599,12 +6599,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>157172</t>
+          <t>158379</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>210748</t>
+          <t>212788</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -6642,12 +6642,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>72162</t>
+          <t>72727</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>111671</t>
+          <t>110434</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6677,12 +6677,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>43564</t>
+          <t>43109</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>72576</t>
+          <t>73274</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>124528</t>
+          <t>122971</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>175587</t>
+          <t>172066</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>46227</t>
+          <t>46544</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>77766</t>
+          <t>76536</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6790,12 +6790,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>39749</t>
+          <t>39070</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>71018</t>
+          <t>68965</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6825,12 +6825,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>94647</t>
+          <t>92696</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>135873</t>
+          <t>135100</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -6868,12 +6868,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>207563</t>
+          <t>208569</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>265555</t>
+          <t>265097</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>106499</t>
+          <t>107046</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>151100</t>
+          <t>148783</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>328097</t>
+          <t>330225</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>400390</t>
+          <t>399568</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -6981,12 +6981,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>456121</t>
+          <t>455877</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>525785</t>
+          <t>528787</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>263037</t>
+          <t>263866</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>322777</t>
+          <t>321326</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>734566</t>
+          <t>733947</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>827258</t>
+          <t>827516</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,57%</t>
         </is>
       </c>
     </row>
@@ -7094,12 +7094,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>241481</t>
+          <t>237949</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>302467</t>
+          <t>299697</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7109,12 +7109,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7129,12 +7129,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>207016</t>
+          <t>207479</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>262604</t>
+          <t>259488</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7164,12 +7164,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>462248</t>
+          <t>463066</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>546679</t>
+          <t>540069</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10874</t>
+          <t>11292</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5611</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>2768</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13696</t>
+          <t>14283</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -7668,12 +7668,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14036</t>
+          <t>13641</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7683,12 +7683,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7703,12 +7703,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10347</t>
+          <t>10645</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6402</t>
+          <t>7194</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20046</t>
+          <t>20551</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -7781,12 +7781,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11858</t>
+          <t>11752</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7796,12 +7796,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3844</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14186</t>
+          <t>14277</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7851,12 +7851,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7531</t>
+          <t>7281</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22193</t>
+          <t>21571</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -7894,12 +7894,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24078</t>
+          <t>23423</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45181</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7909,12 +7909,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7929,12 +7929,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>4308</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16092</t>
+          <t>15840</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7964,12 +7964,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32245</t>
+          <t>31509</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56303</t>
+          <t>54413</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>29,51%</t>
         </is>
       </c>
     </row>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35074</t>
+          <t>35558</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56586</t>
+          <t>57745</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8022,12 +8022,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11116</t>
+          <t>10993</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24835</t>
+          <t>25198</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>50472</t>
+          <t>50595</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>75772</t>
+          <t>77653</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>42,11%</t>
         </is>
       </c>
     </row>
@@ -8120,12 +8120,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16141</t>
+          <t>16093</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33822</t>
+          <t>33909</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8155,12 +8155,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14282</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29393</t>
+          <t>30624</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>34592</t>
+          <t>34431</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>58656</t>
+          <t>58031</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,47%</t>
         </is>
       </c>
     </row>
@@ -8350,12 +8350,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61660</t>
+          <t>60460</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95919</t>
+          <t>95811</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8365,12 +8365,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8385,12 +8385,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35164</t>
+          <t>35255</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63089</t>
+          <t>62044</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8400,12 +8400,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>104325</t>
+          <t>105645</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>147620</t>
+          <t>147743</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -8463,12 +8463,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34244</t>
+          <t>35383</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>62842</t>
+          <t>62819</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -8498,12 +8498,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17223</t>
+          <t>17312</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36897</t>
+          <t>37399</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>58696</t>
+          <t>57117</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>92959</t>
+          <t>92512</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -8576,12 +8576,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31066</t>
+          <t>30902</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56878</t>
+          <t>57236</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23155</t>
+          <t>22390</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47041</t>
+          <t>44793</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59561</t>
+          <t>58620</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94761</t>
+          <t>93546</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -8689,12 +8689,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>168627</t>
+          <t>172514</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>220057</t>
+          <t>219708</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8704,12 +8704,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>85846</t>
+          <t>87962</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>122301</t>
+          <t>122652</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>269217</t>
+          <t>268255</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>332158</t>
+          <t>329701</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,99%</t>
         </is>
       </c>
     </row>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>323842</t>
+          <t>324785</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>382175</t>
+          <t>382430</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8817,12 +8817,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8837,12 +8837,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>218502</t>
+          <t>218742</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>265598</t>
+          <t>268041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8852,12 +8852,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8872,12 +8872,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>555338</t>
+          <t>557911</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>630273</t>
+          <t>630336</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8887,12 +8887,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,95%</t>
         </is>
       </c>
     </row>
@@ -8915,12 +8915,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>116258</t>
+          <t>117496</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>160289</t>
+          <t>161969</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8930,12 +8930,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8950,12 +8950,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>109596</t>
+          <t>108100</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>147778</t>
+          <t>148966</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8985,12 +8985,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>235759</t>
+          <t>236238</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>294481</t>
+          <t>293566</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9000,12 +9000,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>
@@ -9145,12 +9145,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50578</t>
+          <t>49827</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>78064</t>
+          <t>78975</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9160,12 +9160,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9180,12 +9180,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44903</t>
+          <t>44253</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>72664</t>
+          <t>71439</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>103091</t>
+          <t>102945</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>143357</t>
+          <t>142068</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -9258,12 +9258,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10023</t>
+          <t>9945</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28146</t>
+          <t>28463</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9273,12 +9273,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9293,12 +9293,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12654</t>
+          <t>12866</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29439</t>
+          <t>30100</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9308,12 +9308,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9328,12 +9328,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26378</t>
+          <t>26186</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>50282</t>
+          <t>51073</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -9371,12 +9371,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22447</t>
+          <t>22527</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45028</t>
+          <t>45632</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9386,12 +9386,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9406,12 +9406,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>8886</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22977</t>
+          <t>22653</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9421,12 +9421,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9441,12 +9441,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>35505</t>
+          <t>35604</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>61836</t>
+          <t>63092</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9456,12 +9456,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -9484,12 +9484,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52161</t>
+          <t>51217</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>82529</t>
+          <t>82953</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9499,12 +9499,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9519,12 +9519,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>54678</t>
+          <t>54731</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>83778</t>
+          <t>81741</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9534,12 +9534,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9554,12 +9554,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>113306</t>
+          <t>112601</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>153895</t>
+          <t>154099</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9569,12 +9569,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,08%</t>
         </is>
       </c>
     </row>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>71220</t>
+          <t>69933</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>103028</t>
+          <t>102503</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9632,12 +9632,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>61382</t>
+          <t>62568</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91538</t>
+          <t>91562</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9647,12 +9647,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>140097</t>
+          <t>139714</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>183944</t>
+          <t>185453</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,59%</t>
         </is>
       </c>
     </row>
@@ -9710,12 +9710,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29802</t>
+          <t>29423</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>53834</t>
+          <t>55022</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9725,12 +9725,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>18344</t>
+          <t>18594</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>38107</t>
+          <t>39663</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9760,12 +9760,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9780,12 +9780,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>53556</t>
+          <t>52925</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>84790</t>
+          <t>84147</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -9940,12 +9940,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>125433</t>
+          <t>124671</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>170875</t>
+          <t>171510</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9955,12 +9955,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9975,12 +9975,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>89071</t>
+          <t>88770</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>129788</t>
+          <t>129143</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9990,12 +9990,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>225667</t>
+          <t>225973</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>286009</t>
+          <t>284559</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -10053,12 +10053,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>56499</t>
+          <t>56835</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>92513</t>
+          <t>91012</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10088,12 +10088,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>38828</t>
+          <t>38255</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>67683</t>
+          <t>66137</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10103,12 +10103,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>104535</t>
+          <t>103062</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>146780</t>
+          <t>145361</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -10166,12 +10166,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>62822</t>
+          <t>65647</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>100035</t>
+          <t>100643</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10181,12 +10181,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>42287</t>
+          <t>42706</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>72128</t>
+          <t>72723</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10216,12 +10216,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>113645</t>
+          <t>114105</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>160381</t>
+          <t>158202</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -10279,12 +10279,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>262438</t>
+          <t>265918</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>321924</t>
+          <t>326649</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10294,12 +10294,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>158213</t>
+          <t>157773</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>206556</t>
+          <t>205281</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10329,12 +10329,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10349,12 +10349,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>435683</t>
+          <t>436404</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>515037</t>
+          <t>514557</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10364,12 +10364,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>446012</t>
+          <t>447118</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>518819</t>
+          <t>518168</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10427,12 +10427,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>306927</t>
+          <t>307974</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>366366</t>
+          <t>367319</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10442,12 +10442,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10462,12 +10462,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>770960</t>
+          <t>778706</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>867043</t>
+          <t>870017</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10477,12 +10477,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,77%</t>
         </is>
       </c>
     </row>
@@ -10505,12 +10505,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>178506</t>
+          <t>177778</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>228517</t>
+          <t>229497</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10520,12 +10520,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10540,12 +10540,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>152938</t>
+          <t>151471</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>201267</t>
+          <t>200980</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10555,12 +10555,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10575,12 +10575,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>342613</t>
+          <t>342703</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>414946</t>
+          <t>417857</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10590,12 +10590,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -10961,32 +10961,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11228</t>
+          <t>11075</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10996,32 +10996,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3466</t>
+          <t>3701</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8023</t>
+          <t>7615</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11031,32 +11031,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7977</t>
+          <t>8320</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>4136</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15026</t>
+          <t>14807</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -11074,32 +11074,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10323</t>
+          <t>11039</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11109,32 +11109,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6611</t>
+          <t>7134</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11144,32 +11144,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>7863</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14537</t>
+          <t>14503</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -11187,32 +11187,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>8661</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3535</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17399</t>
+          <t>19145</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11222,32 +11222,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4643</t>
+          <t>5946</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9293</t>
+          <t>10839</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11257,32 +11257,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>12755</t>
+          <t>14607</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>8813</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21918</t>
+          <t>24970</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -11300,32 +11300,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>43854</t>
+          <t>51797</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32962</t>
+          <t>39167</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55828</t>
+          <t>65013</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11335,32 +11335,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>13686</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>8517</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17464</t>
+          <t>20668</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11370,32 +11370,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>55275</t>
+          <t>65483</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42001</t>
+          <t>51977</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70379</t>
+          <t>79818</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>34,28%</t>
         </is>
       </c>
     </row>
@@ -11413,32 +11413,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>39267</t>
+          <t>55565</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28594</t>
+          <t>43280</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50240</t>
+          <t>69935</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11448,32 +11448,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>23081</t>
+          <t>24863</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16055</t>
+          <t>18423</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30699</t>
+          <t>32939</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11483,32 +11483,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>62349</t>
+          <t>80428</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>50742</t>
+          <t>66660</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>77597</t>
+          <t>95402</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>40,97%</t>
         </is>
       </c>
     </row>
@@ -11526,32 +11526,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20701</t>
+          <t>25280</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13553</t>
+          <t>15898</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32324</t>
+          <t>36997</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11561,32 +11561,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28700</t>
+          <t>30584</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21927</t>
+          <t>23267</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40206</t>
+          <t>38787</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11596,32 +11596,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>49401</t>
+          <t>55864</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>38110</t>
+          <t>42768</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>65631</t>
+          <t>69893</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>30,02%</t>
         </is>
       </c>
     </row>
@@ -11639,17 +11639,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>121207</t>
+          <t>150845</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>121207</t>
+          <t>150845</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>121207</t>
+          <t>150845</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11674,17 +11674,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>74413</t>
+          <t>82012</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74413</t>
+          <t>82012</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74413</t>
+          <t>82012</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11709,17 +11709,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>195621</t>
+          <t>232858</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>195621</t>
+          <t>232858</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>195621</t>
+          <t>232858</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11756,32 +11756,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>101257</t>
+          <t>113811</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83323</t>
+          <t>92512</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>121712</t>
+          <t>138117</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11791,32 +11791,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>70775</t>
+          <t>77745</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50486</t>
+          <t>63689</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90042</t>
+          <t>94701</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11826,32 +11826,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>172032</t>
+          <t>191556</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>142318</t>
+          <t>166671</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>199824</t>
+          <t>220492</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -11869,32 +11869,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>59963</t>
+          <t>62851</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43469</t>
+          <t>46706</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>78184</t>
+          <t>83500</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11904,32 +11904,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>53490</t>
+          <t>56024</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37302</t>
+          <t>44423</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>69127</t>
+          <t>68006</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11939,32 +11939,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>113453</t>
+          <t>118875</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>90910</t>
+          <t>98508</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>138609</t>
+          <t>143368</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -11982,32 +11982,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>115771</t>
+          <t>127299</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95162</t>
+          <t>104605</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>140426</t>
+          <t>151397</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12017,32 +12017,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>62786</t>
+          <t>66972</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44384</t>
+          <t>54302</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79382</t>
+          <t>80805</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12052,32 +12052,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>178557</t>
+          <t>194271</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>149116</t>
+          <t>170154</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>209131</t>
+          <t>224113</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -12095,27 +12095,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>296442</t>
+          <t>333274</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>265301</t>
+          <t>298634</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>330484</t>
+          <t>366958</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -12130,32 +12130,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>199987</t>
+          <t>185687</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>153247</t>
+          <t>165517</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>283203</t>
+          <t>206022</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12165,32 +12165,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>496429</t>
+          <t>518961</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>433026</t>
+          <t>474966</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>568745</t>
+          <t>560713</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -12208,32 +12208,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>288418</t>
+          <t>323099</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>253864</t>
+          <t>285613</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>321213</t>
+          <t>356519</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12243,32 +12243,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>282848</t>
+          <t>242018</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>220104</t>
+          <t>217659</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>434551</t>
+          <t>265452</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12278,32 +12278,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>571266</t>
+          <t>565117</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>506438</t>
+          <t>522325</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>723078</t>
+          <t>602742</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>31,83%</t>
         </is>
       </c>
     </row>
@@ -12321,32 +12321,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>145012</t>
+          <t>157641</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>122893</t>
+          <t>134676</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>171524</t>
+          <t>186599</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12356,32 +12356,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>120996</t>
+          <t>146998</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>83027</t>
+          <t>129871</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>144290</t>
+          <t>168212</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12391,32 +12391,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>266009</t>
+          <t>304640</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>228675</t>
+          <t>274535</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>302504</t>
+          <t>336114</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -12434,17 +12434,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1006863</t>
+          <t>1117975</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1006863</t>
+          <t>1117975</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1006863</t>
+          <t>1117975</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12469,17 +12469,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>790882</t>
+          <t>775445</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>790882</t>
+          <t>775445</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>790882</t>
+          <t>775445</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12504,17 +12504,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1797745</t>
+          <t>1893420</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1797745</t>
+          <t>1893420</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1797745</t>
+          <t>1893420</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12551,32 +12551,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>80905</t>
+          <t>88133</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>64625</t>
+          <t>71177</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>99208</t>
+          <t>108298</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12586,32 +12586,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>72792</t>
+          <t>79772</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>60080</t>
+          <t>66098</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>87783</t>
+          <t>94091</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12621,32 +12621,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>153697</t>
+          <t>167905</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>132712</t>
+          <t>147081</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>175369</t>
+          <t>195829</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -12664,32 +12664,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>34327</t>
+          <t>26630</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20579</t>
+          <t>17267</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>68926</t>
+          <t>40344</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12699,32 +12699,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>29201</t>
+          <t>30920</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21637</t>
+          <t>21762</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40574</t>
+          <t>42925</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12734,32 +12734,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>63528</t>
+          <t>57549</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46951</t>
+          <t>43205</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>91976</t>
+          <t>73518</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -12777,32 +12777,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>31706</t>
+          <t>35990</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21454</t>
+          <t>25313</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45651</t>
+          <t>50833</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12812,32 +12812,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>28311</t>
+          <t>32176</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20678</t>
+          <t>23651</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38619</t>
+          <t>44366</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12847,32 +12847,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>60017</t>
+          <t>68166</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>46480</t>
+          <t>54272</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>76871</t>
+          <t>86492</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -12890,32 +12890,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>100242</t>
+          <t>109065</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>81534</t>
+          <t>90161</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>122681</t>
+          <t>130728</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12925,32 +12925,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>82632</t>
+          <t>88419</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>71122</t>
+          <t>76113</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>96986</t>
+          <t>103984</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -12960,32 +12960,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>182874</t>
+          <t>197484</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>161879</t>
+          <t>172541</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>206735</t>
+          <t>222658</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,89%</t>
         </is>
       </c>
     </row>
@@ -13003,32 +13003,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>68237</t>
+          <t>74820</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52485</t>
+          <t>57768</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>85409</t>
+          <t>93661</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13038,32 +13038,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>86694</t>
+          <t>94019</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>72046</t>
+          <t>78835</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>102724</t>
+          <t>109304</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13073,17 +13073,17 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>154931</t>
+          <t>168839</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>133361</t>
+          <t>148693</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>178331</t>
+          <t>195644</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,51%</t>
         </is>
       </c>
     </row>
@@ -13116,32 +13116,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>62388</t>
+          <t>74324</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>48372</t>
+          <t>58809</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>79864</t>
+          <t>92067</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13151,32 +13151,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>54974</t>
+          <t>64072</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>43560</t>
+          <t>51846</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>67896</t>
+          <t>77021</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13186,32 +13186,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>117362</t>
+          <t>138396</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>99730</t>
+          <t>120309</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>137929</t>
+          <t>162307</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>20,33%</t>
         </is>
       </c>
     </row>
@@ -13229,17 +13229,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>377805</t>
+          <t>408962</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>377805</t>
+          <t>408962</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>377805</t>
+          <t>408962</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13264,17 +13264,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>354604</t>
+          <t>389378</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>354604</t>
+          <t>389378</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>354604</t>
+          <t>389378</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13299,17 +13299,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>732409</t>
+          <t>798340</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>732409</t>
+          <t>798340</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>732409</t>
+          <t>798340</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13346,32 +13346,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>186672</t>
+          <t>206562</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>159541</t>
+          <t>175415</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>215654</t>
+          <t>236508</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13381,32 +13381,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>147033</t>
+          <t>161219</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>113301</t>
+          <t>141464</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>169906</t>
+          <t>184164</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13416,32 +13416,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>333706</t>
+          <t>367781</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>298727</t>
+          <t>334194</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>370656</t>
+          <t>409230</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -13459,32 +13459,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>99052</t>
+          <t>94404</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>77071</t>
+          <t>75171</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>131727</t>
+          <t>118656</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13494,32 +13494,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>85792</t>
+          <t>90176</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>67367</t>
+          <t>75704</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>103853</t>
+          <t>108237</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13529,32 +13529,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>184844</t>
+          <t>184580</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>153603</t>
+          <t>158152</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>217627</t>
+          <t>210799</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -13572,32 +13572,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>155589</t>
+          <t>171950</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>133470</t>
+          <t>144180</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>183199</t>
+          <t>202723</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -13607,32 +13607,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>95740</t>
+          <t>105095</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>75916</t>
+          <t>87636</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>114679</t>
+          <t>123048</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -13642,32 +13642,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>251329</t>
+          <t>277045</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>215981</t>
+          <t>246440</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>285533</t>
+          <t>310603</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -13685,32 +13685,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>440538</t>
+          <t>494136</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>402234</t>
+          <t>450581</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>483272</t>
+          <t>542981</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13720,32 +13720,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>294040</t>
+          <t>287792</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>243392</t>
+          <t>260362</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>368760</t>
+          <t>314658</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13755,32 +13755,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>734578</t>
+          <t>781928</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>670314</t>
+          <t>731062</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>823235</t>
+          <t>835313</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>28,56%</t>
         </is>
       </c>
     </row>
@@ -13798,32 +13798,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>395922</t>
+          <t>453484</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>358239</t>
+          <t>411955</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>435836</t>
+          <t>498866</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13833,32 +13833,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>392624</t>
+          <t>360901</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>332657</t>
+          <t>332479</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>558070</t>
+          <t>393559</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13868,32 +13868,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>788546</t>
+          <t>814385</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>719397</t>
+          <t>763567</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>968063</t>
+          <t>861695</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>29,46%</t>
         </is>
       </c>
     </row>
@@ -13911,32 +13911,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>228101</t>
+          <t>257246</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>199714</t>
+          <t>226925</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>259824</t>
+          <t>290120</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13946,32 +13946,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>204670</t>
+          <t>241654</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>167124</t>
+          <t>216974</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>235028</t>
+          <t>266229</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13981,32 +13981,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>432772</t>
+          <t>498900</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>386218</t>
+          <t>462857</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>473601</t>
+          <t>541041</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>18,5%</t>
         </is>
       </c>
     </row>
@@ -14024,17 +14024,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1505875</t>
+          <t>1677782</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1505875</t>
+          <t>1677782</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1505875</t>
+          <t>1677782</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14059,17 +14059,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1219899</t>
+          <t>1246836</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1219899</t>
+          <t>1246836</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1219899</t>
+          <t>1246836</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14094,17 +14094,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>2725774</t>
+          <t>2924618</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2725774</t>
+          <t>2924618</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2725774</t>
+          <t>2924618</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
